--- a/Docs/GameDesign/05-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/05-开发计划/第一版开发任务表.xlsx
@@ -2600,6 +2600,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>除最终导入验证外，不依赖主工程功能进度。</t>
     </r>
     <r>
@@ -12442,7 +12448,7 @@
         <v>877</v>
       </c>
       <c r="P137" s="20" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="Q137" s="22"/>
       <c r="R137" s="7"/>

--- a/Docs/GameDesign/05-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/05-开发计划/第一版开发任务表.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2666" uniqueCount="1181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2668" uniqueCount="1183">
   <si>
     <t>第一版开发任务表使用说明</t>
   </si>
@@ -2682,6 +2682,9 @@
     <t>用同一对象完成候选路线对照，最终路线具备明确预算和可重复制作流程。</t>
   </si>
   <si>
+    <t>2026-08-27：G02–G05技术合同与Blender路线已完成并通过制作人验收；G02白模制作中。</t>
+  </si>
+  <si>
     <t>ART-005</t>
   </si>
   <si>
@@ -2698,6 +2701,9 @@
   </si>
   <si>
     <t>形成动作实现矩阵，每类核心动作都明确实现方式、输入参数、循环与中断规则。</t>
+  </si>
+  <si>
+    <t>2026-08-27：G07–G11技术合同与Blender路线已完成并通过制作人验收；等待按顺序进入白模制作。</t>
   </si>
   <si>
     <t>ART-006</t>
@@ -12399,11 +12405,13 @@
         <v>71</v>
       </c>
       <c r="Q136" s="22"/>
-      <c r="R136" s="7"/>
+      <c r="R136" s="28" t="s">
+        <v>872</v>
+      </c>
     </row>
     <row r="137" ht="24" customHeight="1" spans="1:18">
       <c r="A137" s="7" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>133</v>
@@ -12412,16 +12420,16 @@
         <v>134</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G137" s="19" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H137" s="20" t="s">
         <v>51</v>
@@ -12445,17 +12453,19 @@
         <v>112</v>
       </c>
       <c r="O137" s="7" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="P137" s="20" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="Q137" s="22"/>
-      <c r="R137" s="7"/>
+      <c r="R137" s="28" t="s">
+        <v>879</v>
+      </c>
     </row>
     <row r="138" ht="24" customHeight="1" spans="1:18">
       <c r="A138" s="7" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B138" s="7" t="s">
         <v>133</v>
@@ -12464,16 +12474,16 @@
         <v>134</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="G138" s="7" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="H138" s="20" t="s">
         <v>51</v>
@@ -12497,7 +12507,7 @@
         <v>112</v>
       </c>
       <c r="O138" s="7" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="P138" s="20" t="s">
         <v>71</v>
@@ -12507,7 +12517,7 @@
     </row>
     <row r="139" ht="24" customHeight="1" spans="1:18">
       <c r="A139" s="7" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>133</v>
@@ -12519,19 +12529,19 @@
         <v>847</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="G139" s="7" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="H139" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I139" s="7" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="J139" s="20" t="s">
         <v>851</v>
@@ -12549,7 +12559,7 @@
         <v>112</v>
       </c>
       <c r="O139" s="7" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="P139" s="20" t="s">
         <v>92</v>
@@ -12559,7 +12569,7 @@
     </row>
     <row r="140" ht="24" customHeight="1" spans="1:18">
       <c r="A140" s="7" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B140" s="7" t="s">
         <v>133</v>
@@ -12568,22 +12578,22 @@
         <v>134</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="G140" s="7" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="H140" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I140" s="7" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="J140" s="20" t="s">
         <v>153</v>
@@ -12601,19 +12611,19 @@
         <v>112</v>
       </c>
       <c r="O140" s="7" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="P140" s="20" t="s">
         <v>92</v>
       </c>
       <c r="Q140" s="22"/>
       <c r="R140" s="7" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="141" ht="24" customHeight="1" spans="1:18">
       <c r="A141" s="7" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>133</v>
@@ -12622,22 +12632,22 @@
         <v>134</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="G141" s="19" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="H141" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="J141" s="20" t="s">
         <v>153</v>
@@ -12655,19 +12665,19 @@
         <v>112</v>
       </c>
       <c r="O141" s="19" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="P141" s="20" t="s">
         <v>92</v>
       </c>
       <c r="Q141" s="22"/>
       <c r="R141" s="7" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
     </row>
     <row r="142" ht="24" customHeight="1" spans="1:18">
       <c r="A142" s="7" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B142" s="7" t="s">
         <v>133</v>
@@ -12676,25 +12686,25 @@
         <v>134</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="G142" s="7" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="H142" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="J142" s="20" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="K142" s="21">
         <v>4</v>
@@ -12709,7 +12719,7 @@
         <v>112</v>
       </c>
       <c r="O142" s="7" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="P142" s="20" t="s">
         <v>92</v>
@@ -12719,34 +12729,34 @@
     </row>
     <row r="143" ht="24" customHeight="1" spans="1:18">
       <c r="A143" s="7" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D143" s="7" t="s">
         <v>861</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="G143" s="7" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="H143" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="J143" s="20" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="K143" s="21">
         <v>10</v>
@@ -12761,7 +12771,7 @@
         <v>112</v>
       </c>
       <c r="O143" s="7" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="P143" s="20" t="s">
         <v>92</v>
@@ -12771,34 +12781,34 @@
     </row>
     <row r="144" ht="24" customHeight="1" spans="1:18">
       <c r="A144" s="7" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D144" s="7" t="s">
         <v>861</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="G144" s="7" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="H144" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="J144" s="20" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="K144" s="21">
         <v>10</v>
@@ -12813,7 +12823,7 @@
         <v>112</v>
       </c>
       <c r="O144" s="7" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="P144" s="20" t="s">
         <v>92</v>
@@ -12823,34 +12833,34 @@
     </row>
     <row r="145" ht="24" customHeight="1" spans="1:18">
       <c r="A145" s="7" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D145" s="7" t="s">
         <v>861</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="G145" s="7" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="H145" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="J145" s="20" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="K145" s="21">
         <v>12</v>
@@ -12865,7 +12875,7 @@
         <v>112</v>
       </c>
       <c r="O145" s="7" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="P145" s="20" t="s">
         <v>92</v>
@@ -12875,34 +12885,34 @@
     </row>
     <row r="146" ht="24" customHeight="1" spans="1:18">
       <c r="A146" s="7" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D146" s="7" t="s">
         <v>861</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="H146" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="J146" s="20" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="K146" s="21">
         <v>12</v>
@@ -12917,7 +12927,7 @@
         <v>112</v>
       </c>
       <c r="O146" s="7" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="P146" s="20" t="s">
         <v>92</v>
@@ -12927,34 +12937,34 @@
     </row>
     <row r="147" ht="24" customHeight="1" spans="1:18">
       <c r="A147" s="7" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="G147" s="7" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="H147" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="J147" s="20" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="K147" s="21">
         <v>8</v>
@@ -12969,7 +12979,7 @@
         <v>112</v>
       </c>
       <c r="O147" s="7" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="P147" s="20" t="s">
         <v>92</v>
@@ -12979,13 +12989,13 @@
     </row>
     <row r="148" ht="24" customHeight="1" spans="1:18">
       <c r="A148" s="7" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D148" s="7" t="s">
         <v>867</v>
@@ -12994,19 +13004,19 @@
         <v>225</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="G148" s="7" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="H148" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="J148" s="20" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="K148" s="21">
         <v>12</v>
@@ -13021,7 +13031,7 @@
         <v>112</v>
       </c>
       <c r="O148" s="7" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="P148" s="20" t="s">
         <v>92</v>
@@ -13031,34 +13041,34 @@
     </row>
     <row r="149" ht="24" customHeight="1" spans="1:18">
       <c r="A149" s="7" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D149" s="7" t="s">
         <v>867</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="G149" s="7" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="H149" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="J149" s="20" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="K149" s="21">
         <v>12</v>
@@ -13073,7 +13083,7 @@
         <v>112</v>
       </c>
       <c r="O149" s="7" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="P149" s="20" t="s">
         <v>92</v>
@@ -13083,13 +13093,13 @@
     </row>
     <row r="150" ht="24" customHeight="1" spans="1:18">
       <c r="A150" s="7" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D150" s="7" t="s">
         <v>867</v>
@@ -13098,19 +13108,19 @@
         <v>435</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="G150" s="7" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="H150" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="J150" s="20" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="K150" s="21">
         <v>12</v>
@@ -13125,7 +13135,7 @@
         <v>112</v>
       </c>
       <c r="O150" s="7" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="P150" s="20" t="s">
         <v>92</v>
@@ -13135,34 +13145,34 @@
     </row>
     <row r="151" ht="24" customHeight="1" spans="1:18">
       <c r="A151" s="7" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D151" s="7" t="s">
         <v>867</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="G151" s="7" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="H151" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="J151" s="20" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="K151" s="21">
         <v>12</v>
@@ -13177,7 +13187,7 @@
         <v>112</v>
       </c>
       <c r="O151" s="7" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="P151" s="20" t="s">
         <v>92</v>
@@ -13187,13 +13197,13 @@
     </row>
     <row r="152" ht="24" customHeight="1" spans="1:18">
       <c r="A152" s="7" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D152" s="7" t="s">
         <v>867</v>
@@ -13202,19 +13212,19 @@
         <v>411</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="G152" s="7" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="H152" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="J152" s="20" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="K152" s="21">
         <v>12</v>
@@ -13229,7 +13239,7 @@
         <v>112</v>
       </c>
       <c r="O152" s="7" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="P152" s="20" t="s">
         <v>92</v>
@@ -13239,34 +13249,34 @@
     </row>
     <row r="153" ht="24" customHeight="1" spans="1:18">
       <c r="A153" s="7" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="E153" s="7" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="H153" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="J153" s="20" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="K153" s="21">
         <v>10</v>
@@ -13281,7 +13291,7 @@
         <v>112</v>
       </c>
       <c r="O153" s="7" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="P153" s="20" t="s">
         <v>92</v>
@@ -13291,34 +13301,34 @@
     </row>
     <row r="154" ht="24" customHeight="1" spans="1:18">
       <c r="A154" s="7" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D154" s="7" t="s">
         <v>867</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="G154" s="7" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="H154" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="J154" s="20" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="K154" s="21">
         <v>8</v>
@@ -13333,7 +13343,7 @@
         <v>112</v>
       </c>
       <c r="O154" s="7" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="P154" s="20" t="s">
         <v>92</v>
@@ -13343,34 +13353,34 @@
     </row>
     <row r="155" ht="24" customHeight="1" spans="1:18">
       <c r="A155" s="7" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E155" s="7" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="G155" s="7" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="H155" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="J155" s="20" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="K155" s="21">
         <v>10</v>
@@ -13385,7 +13395,7 @@
         <v>112</v>
       </c>
       <c r="O155" s="7" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="P155" s="20" t="s">
         <v>92</v>
@@ -13395,34 +13405,34 @@
     </row>
     <row r="156" ht="24" customHeight="1" spans="1:18">
       <c r="A156" s="7" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D156" s="7" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="G156" s="7" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="H156" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="J156" s="20" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="K156" s="21">
         <v>12</v>
@@ -13437,7 +13447,7 @@
         <v>112</v>
       </c>
       <c r="O156" s="7" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="P156" s="20" t="s">
         <v>92</v>
@@ -13447,34 +13457,34 @@
     </row>
     <row r="157" ht="24" customHeight="1" spans="1:18">
       <c r="A157" s="7" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D157" s="7" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="G157" s="7" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="H157" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="J157" s="20" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="K157" s="21">
         <v>10</v>
@@ -13489,7 +13499,7 @@
         <v>112</v>
       </c>
       <c r="O157" s="7" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="P157" s="20" t="s">
         <v>92</v>
@@ -13499,34 +13509,34 @@
     </row>
     <row r="158" ht="36" customHeight="1" spans="1:18">
       <c r="A158" s="7" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D158" s="7" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E158" s="7" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="G158" s="7" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="H158" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="J158" s="20" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="K158" s="21">
         <v>12</v>
@@ -13541,7 +13551,7 @@
         <v>112</v>
       </c>
       <c r="O158" s="7" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="P158" s="20" t="s">
         <v>92</v>
@@ -13551,34 +13561,34 @@
     </row>
     <row r="159" ht="24" customHeight="1" spans="1:18">
       <c r="A159" s="7" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D159" s="7" t="s">
         <v>292</v>
       </c>
       <c r="E159" s="7" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="G159" s="7" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="H159" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I159" s="7" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="J159" s="20" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="K159" s="21">
         <v>10</v>
@@ -13593,7 +13603,7 @@
         <v>112</v>
       </c>
       <c r="O159" s="7" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="P159" s="20" t="s">
         <v>92</v>
@@ -13603,34 +13613,34 @@
     </row>
     <row r="160" ht="24" customHeight="1" spans="1:18">
       <c r="A160" s="7" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D160" s="7" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="E160" s="7" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="G160" s="7" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="H160" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I160" s="7" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="J160" s="20" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="K160" s="21">
         <v>12</v>
@@ -13645,7 +13655,7 @@
         <v>112</v>
       </c>
       <c r="O160" s="7" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="P160" s="20" t="s">
         <v>92</v>
@@ -13655,34 +13665,34 @@
     </row>
     <row r="161" ht="24" customHeight="1" spans="1:18">
       <c r="A161" s="7" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="E161" s="7" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="G161" s="7" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="H161" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="J161" s="20" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="K161" s="21">
         <v>12</v>
@@ -13697,7 +13707,7 @@
         <v>112</v>
       </c>
       <c r="O161" s="7" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="P161" s="20" t="s">
         <v>92</v>
@@ -13707,34 +13717,34 @@
     </row>
     <row r="162" ht="24" customHeight="1" spans="1:18">
       <c r="A162" s="7" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="E162" s="7" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="G162" s="7" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="H162" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="J162" s="20" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="K162" s="21">
         <v>10</v>
@@ -13749,7 +13759,7 @@
         <v>112</v>
       </c>
       <c r="O162" s="7" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="P162" s="20" t="s">
         <v>92</v>
@@ -13759,34 +13769,34 @@
     </row>
     <row r="163" ht="24" customHeight="1" spans="1:18">
       <c r="A163" s="7" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="D163" s="7" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="G163" s="7" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="H163" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="J163" s="20" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="K163" s="21">
         <v>6</v>
@@ -13801,7 +13811,7 @@
         <v>112</v>
       </c>
       <c r="O163" s="7" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="P163" s="20" t="s">
         <v>92</v>
@@ -13811,34 +13821,34 @@
     </row>
     <row r="164" ht="36" customHeight="1" spans="1:18">
       <c r="A164" s="7" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="E164" s="7" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="G164" s="7" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="H164" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="J164" s="20" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="K164" s="21">
         <v>12</v>
@@ -13853,46 +13863,46 @@
         <v>112</v>
       </c>
       <c r="O164" s="7" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="P164" s="20" t="s">
         <v>92</v>
       </c>
       <c r="Q164" s="22"/>
       <c r="R164" s="7" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="165" ht="24" customHeight="1" spans="1:18">
       <c r="A165" s="7" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="D165" s="7" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="G165" s="19" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="H165" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="J165" s="20" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="K165" s="21">
         <v>12</v>
@@ -13907,46 +13917,46 @@
         <v>112</v>
       </c>
       <c r="O165" s="7" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="P165" s="20" t="s">
         <v>92</v>
       </c>
       <c r="Q165" s="22"/>
       <c r="R165" s="7" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="166" ht="24" customHeight="1" spans="1:18">
       <c r="A166" s="7" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="D166" s="7" t="s">
         <v>861</v>
       </c>
       <c r="E166" s="7" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="G166" s="7" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="H166" s="20" t="s">
         <v>51</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="J166" s="20" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="K166" s="21">
         <v>8</v>
@@ -13961,7 +13971,7 @@
         <v>112</v>
       </c>
       <c r="O166" s="7" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="P166" s="20" t="s">
         <v>92</v>
@@ -13971,34 +13981,34 @@
     </row>
     <row r="167" ht="25.5" spans="1:18">
       <c r="A167" s="7" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="E167" s="7" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="G167" s="7" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="H167" s="7" t="s">
         <v>51</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="J167" s="7" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="K167" s="29">
         <v>10</v>
@@ -14013,7 +14023,7 @@
         <v>112</v>
       </c>
       <c r="O167" s="7" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="P167" s="7" t="s">
         <v>92</v>
@@ -14023,34 +14033,34 @@
     </row>
     <row r="168" ht="25.5" spans="1:18">
       <c r="A168" s="7" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="D168" s="7" t="s">
         <v>847</v>
       </c>
       <c r="E168" s="7" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="G168" s="7" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="H168" s="7" t="s">
         <v>51</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="J168" s="7" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="K168" s="29">
         <v>10</v>
@@ -14065,7 +14075,7 @@
         <v>112</v>
       </c>
       <c r="O168" s="7" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="P168" s="7" t="s">
         <v>92</v>
@@ -14075,34 +14085,34 @@
     </row>
     <row r="169" ht="25.5" spans="1:18">
       <c r="A169" s="7" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="D169" s="7" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="E169" s="7" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="G169" s="7" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="H169" s="7" t="s">
         <v>51</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="J169" s="7" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="K169" s="29">
         <v>6</v>
@@ -14117,7 +14127,7 @@
         <v>112</v>
       </c>
       <c r="O169" s="7" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="P169" s="7" t="s">
         <v>92</v>
@@ -14127,7 +14137,7 @@
     </row>
     <row r="170" ht="25.5" spans="1:18">
       <c r="A170" s="7" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="B170" s="7" t="s">
         <v>760</v>
@@ -14139,22 +14149,22 @@
         <v>126</v>
       </c>
       <c r="E170" s="7" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="G170" s="7" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="H170" s="7" t="s">
         <v>51</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="J170" s="7" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="K170" s="29">
         <v>14</v>
@@ -14169,7 +14179,7 @@
         <v>55</v>
       </c>
       <c r="O170" s="7" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="P170" s="7" t="s">
         <v>92</v>
@@ -14222,7 +14232,7 @@
         <v>28</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>36</v>
@@ -14231,10 +14241,10 @@
         <v>37</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="2" ht="24.75" spans="1:7">
@@ -14465,10 +14475,10 @@
         <v>234</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="11" ht="24" spans="1:7">
@@ -14491,18 +14501,18 @@
         <v>182</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="C12" s="7">
         <f>COUNTIF(开发任务!$B$2:$B$170,A12)</f>
@@ -14517,18 +14527,18 @@
         <v>300</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="7" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="C13" s="7">
         <f>COUNTIF(开发任务!$B$2:$B$170,A13)</f>
@@ -14543,10 +14553,10 @@
         <v>138</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
     </row>
   </sheetData>
@@ -14574,7 +14584,7 @@
         <v>29</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>36</v>
@@ -14586,7 +14596,7 @@
         <v>39</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -14609,7 +14619,7 @@
         <v>55</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -14632,7 +14642,7 @@
         <v>55</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -14655,7 +14665,7 @@
         <v>55</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="5" ht="24" spans="1:6">
@@ -14678,7 +14688,7 @@
         <v>112</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -14701,7 +14711,7 @@
         <v>55</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="7" ht="24" spans="1:6">
@@ -14724,7 +14734,7 @@
         <v>112</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="8" ht="24" spans="1:6">
@@ -14747,7 +14757,7 @@
         <v>112</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="9" ht="24" spans="1:6">
@@ -14770,7 +14780,7 @@
         <v>112</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="10" ht="24" spans="1:6">
@@ -14793,7 +14803,7 @@
         <v>112</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="11" ht="24" spans="1:6">
@@ -14816,12 +14826,12 @@
         <v>112</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="12" ht="24" spans="1:6">
       <c r="A12" s="7" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B12" s="7">
         <f>COUNTIF(开发任务!$D$2:$D$170,A12)</f>
@@ -14839,12 +14849,12 @@
         <v>112</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="13" ht="24" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B13" s="7">
         <f>COUNTIF(开发任务!$D$2:$D$170,A13)</f>
@@ -14862,12 +14872,12 @@
         <v>112</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="14" ht="24" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B14" s="7">
         <f>COUNTIF(开发任务!$D$2:$D$170,A14)</f>
@@ -14885,7 +14895,7 @@
         <v>112</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
     </row>
   </sheetData>
@@ -14912,7 +14922,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:6">
       <c r="A1" s="9" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -14922,7 +14932,7 @@
     </row>
     <row r="2" ht="34" customHeight="1" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -14932,19 +14942,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="10" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>43</v>
@@ -14952,7 +14962,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="11" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="B4" s="6">
         <f>COUNTA(开发任务!$A$2:$A$170)</f>
@@ -14960,16 +14970,16 @@
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="F4" s="6"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="13" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="B5" s="7">
         <f>SUMIF(开发任务!$N$2:$N$170,"程序预算",开发任务!$K$2:$K$170)</f>
@@ -14984,13 +14994,13 @@
         <v>122项</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="13" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="B6" s="7">
         <f>SUMIF(开发任务!$N$2:$N$170,"美术资源预算",开发任务!$K$2:$K$170)</f>
@@ -15005,15 +15015,15 @@
         <v>47项</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="13" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="B7" s="7">
         <f>SUM(开发任务!$K$2:$K$170)</f>
@@ -15024,16 +15034,16 @@
         <v>2650</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="13" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="B8" s="7">
         <f>MAX(开发任务!$L$2:$L$170)</f>
@@ -15043,28 +15053,28 @@
         <v>18</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="13" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="F9" s="7"/>
     </row>
@@ -15093,33 +15103,33 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:5">
       <c r="A1" s="3" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="6" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>399</v>
@@ -15127,16 +15137,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="7" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>757</v>
@@ -15144,104 +15154,104 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="7" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="7" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>1140</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="8" ht="24" spans="1:5">
       <c r="A8" s="7" t="s">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="7" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
     </row>
   </sheetData>
@@ -15267,7 +15277,7 @@
   <sheetData>
     <row r="1" ht="21" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -15277,7 +15287,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -15287,22 +15297,22 @@
     </row>
     <row r="4" ht="27" spans="1:6">
       <c r="A4" s="3" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="5" ht="56" customHeight="1" spans="1:6">
@@ -15310,59 +15320,59 @@
         <v>133</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="6" ht="56" customHeight="1" spans="1:6">
       <c r="A6" s="7" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="7" ht="56" customHeight="1" spans="1:6">
       <c r="A7" s="8" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -15370,7 +15380,7 @@
         <v>29</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>36</v>
@@ -15379,10 +15389,10 @@
         <v>37</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -15402,10 +15412,10 @@
         <v>54</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -15425,10 +15435,10 @@
         <v>98</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -15448,15 +15458,15 @@
         <v>116</v>
       </c>
       <c r="E12" s="7" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>1175</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="7" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B13" s="7">
         <f>COUNTIF(开发任务!$D$2:$D$170,A13)</f>
@@ -15471,10 +15481,10 @@
         <v>84</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -15494,15 +15504,15 @@
         <v>66</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B15" s="7">
         <f>COUNTIF(开发任务!$D$2:$D$170,A15)</f>
@@ -15517,15 +15527,15 @@
         <v>50</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="16" ht="25.5" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B16" s="7">
         <f>COUNTIF(开发任务!$D$2:$D$170,A16)</f>
@@ -15540,10 +15550,10 @@
         <v>148</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -15563,10 +15573,10 @@
         <v>96</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -15586,10 +15596,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
     </row>
   </sheetData>
